--- a/CompareKPI_United/templates/template_MMT.xlsx
+++ b/CompareKPI_United/templates/template_MMT.xlsx
@@ -1247,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.27272727272727" customWidth="1" style="24" min="1" max="1"/>
@@ -2041,9 +2041,60 @@
       <c r="G40" s="19" t="n"/>
       <c r="H40" s="19" t="n"/>
     </row>
-    <row r="41" s="24"/>
-    <row r="42" s="24"/>
-    <row r="43" s="24"/>
+    <row r="41" s="24">
+      <c r="A41" s="28" t="n"/>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>ABS触发关联ACC退出</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="29" t="inlineStr">
+        <is>
+          <t>ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="n"/>
+      <c r="F41" s="19" t="n"/>
+      <c r="G41" s="19" t="n"/>
+      <c r="H41" s="19" t="n"/>
+    </row>
+    <row r="42" s="24">
+      <c r="A42" s="28" t="n"/>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>TCS触发关联ACC退出</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="29" t="inlineStr">
+        <is>
+          <t>TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="19" t="n"/>
+      <c r="H42" s="19" t="n"/>
+    </row>
+    <row r="43" s="24">
+      <c r="A43" s="28" t="n"/>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>VSE触发关联ACC退出</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="29" t="inlineStr">
+        <is>
+          <t>VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="19" t="n"/>
+      <c r="H43" s="19" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="G2:H2"/>

--- a/CompareKPI_United/templates/template_MMT.xlsx
+++ b/CompareKPI_United/templates/template_MMT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="11950" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,30 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MPI/CPI ????</author>
+  </authors>
+  <commentList>
+    <comment ref="D5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>?????? PHEV/BEV ? ICE ???????????????????????????????????????</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="113">
   <si>
     <t>车型</t>
   </si>
@@ -85,25 +107,29 @@
     <t>行车-静止起步到稳速</t>
   </si>
   <si>
-    <t>1.0~3.0m/s2</t>
+    <t>PHEV/BEV：1.0~2.7m/s2
+ICE：1.0~2.7m/s2</t>
   </si>
   <si>
     <t>起步最大jerk</t>
   </si>
   <si>
-    <t>&lt;=3.5m/s3</t>
+    <t>PHEV/BEV：&lt;=3.5m/s3
+ICE：&lt;=4m/s3</t>
   </si>
   <si>
     <t>初段建立时间</t>
   </si>
   <si>
-    <t>达到3.33m/s所需时间：1.0~3.5s</t>
+    <t>PHEV/BEV：达到3.33m/s所需时间：1.0~2.8s
+ICE：达到3.33m/s所需时间：1.0~3.2s</t>
   </si>
   <si>
     <t>起步加速建立时间</t>
   </si>
   <si>
-    <t>首次acc&gt;0.2到最大acc：1.0~4.0s</t>
+    <t>PHEV/BEV：首次acc&gt;0.2到最大acc：1.0~3.5s
+ICE：首次acc&gt;0.2到最大acc：1.0~4.0s</t>
   </si>
   <si>
     <t>弯道安全速度</t>
@@ -112,19 +138,22 @@
     <t>行车-弯道稳速</t>
   </si>
   <si>
-    <t>sqrt(1.0*R)-2 ~ sqrt(2.9*R)+2m/s；SetSpeed&lt;=sqrt(1.0*R)不判bad</t>
+    <t>PHEV/BEV：sqrt(1.0*R)-2 ~ sqrt(2.9*R)+2m/s；SetSpeed&lt;=sqrt(1.0*R)不判bad
+ICE：sqrt(1.0*R)-2 ~ sqrt(2.9*R)+2m/s；SetSpeed&lt;=sqrt(1.0*R)不判bad</t>
   </si>
   <si>
     <t>弯道限速最大减速度</t>
   </si>
   <si>
-    <t>&gt;=-2m/s2</t>
+    <t>PHEV/BEV：&gt;=-2m/s2
+ICE：&gt;=-2m/s2</t>
   </si>
   <si>
     <t>弯道限速减速舒适性</t>
   </si>
   <si>
-    <t>&gt;=-2m/s3</t>
+    <t>PHEV/BEV：&gt;=-2m/s3
+ICE：&gt;=-2m/s3</t>
   </si>
   <si>
     <t>坡道稳速抖动</t>
@@ -133,19 +162,22 @@
     <t>行车-坡道稳速</t>
   </si>
   <si>
-    <t>速度波动&lt;=1m/s</t>
+    <t>PHEV/BEV：速度波动&lt;=0.3m/s
+ICE：速度波动&lt;=0.6m/s</t>
   </si>
   <si>
     <t>坡道控速稳定性</t>
   </si>
   <si>
-    <t>|加速度|&lt;=0.75m/s2</t>
+    <t>PHEV/BEV：|加速度|&lt;=0.75m/s2
+ICE：|加速度|&lt;=0.75m/s2</t>
   </si>
   <si>
     <t>坡道控速舒适性</t>
   </si>
   <si>
-    <t>|jerk|&lt;=1m/s3</t>
+    <t>PHEV/BEV：|jerk|&lt;=1m/s3
+ICE：|jerk|&lt;=1m/s3</t>
   </si>
   <si>
     <t>跟车刹停最大减速度</t>
@@ -154,13 +186,15 @@
     <t>行车-跟车刹停</t>
   </si>
   <si>
-    <t>&gt;=max(min(-初始速度(m/s)/5.5,-1.75),-4)-1m/s2</t>
+    <t>PHEV/BEV：&gt;=max(min(-初始速度(m/s)/5.5,-1.75),-4)-1m/s2
+ICE：&gt;=max(min(-初始速度(m/s)/5.5,-1.75),-4)-1m/s2</t>
   </si>
   <si>
     <t>跟车刹停距离</t>
   </si>
   <si>
-    <t>2~5m</t>
+    <t>PHEV/BEV：刹停完成时距前车距离：3~4m
+ICE：刹停完成时距前车距离：3~4m</t>
   </si>
   <si>
     <t>跟车刹停舒适性</t>
@@ -169,19 +203,22 @@
     <t>跟车刹停反应</t>
   </si>
   <si>
-    <t>TTC&gt;=2.5s</t>
+    <t>PHEV/BEV：TTC&gt;=4.5s
+ICE：TTC&gt;=4.5s</t>
   </si>
   <si>
     <t>跟车刹停风险</t>
   </si>
   <si>
-    <t>TTC&gt;=1.5s</t>
+    <t>PHEV/BEV：TTC&gt;=1.5s
+ICE：TTC&gt;=1.5s</t>
   </si>
   <si>
     <t>跟车刹停波动</t>
   </si>
   <si>
-    <t>&lt;=3次</t>
+    <t>PHEV/BEV：&lt;=3次
+ICE：&lt;=3次</t>
   </si>
   <si>
     <t>跟车起步响应时延</t>
@@ -190,13 +227,15 @@
     <t>行车-跟车起步</t>
   </si>
   <si>
-    <t>&lt;=2.5s</t>
+    <t>PHEV/BEV：&lt;=2.5s
+ICE：&lt;=2.8s</t>
   </si>
   <si>
     <t>跟车起步舒适性</t>
   </si>
   <si>
-    <t>1.0~2.5m/s3</t>
+    <t>PHEV/BEV：1.0~1.5m/s3
+ICE：1.0~1.5m/s3</t>
   </si>
   <si>
     <t>红灯刹停距停止线距离</t>
@@ -205,121 +244,147 @@
     <t>行车-红灯刹停</t>
   </si>
   <si>
-    <t>0~4m</t>
+    <t>PHEV/BEV：1.5~3.5m
+ICE：1.5~3.5m</t>
   </si>
   <si>
     <t>红灯刹停舒适性</t>
   </si>
   <si>
+    <t>PHEV/BEV：&gt;=-2m/s3
+ICE：&gt;=-2.3m/s3</t>
+  </si>
+  <si>
     <t>绿灯起步响应时延</t>
   </si>
   <si>
     <t>行车-绿灯起步</t>
   </si>
   <si>
-    <t>&lt;=2.0s</t>
+    <t>PHEV/BEV：&lt;=1.5s
+ICE：&lt;=1.7s</t>
   </si>
   <si>
     <t>绿灯起步最大加速度</t>
   </si>
   <si>
-    <t>1.0~2.3m/s2</t>
+    <t>PHEV/BEV：1.0~2.3m/s2
+ICE：1.0~2.3m/s2</t>
   </si>
   <si>
     <t>绿灯起步加速时间</t>
   </si>
   <si>
-    <t>&lt;=6.0s</t>
+    <t>PHEV/BEV：&lt;=6.0s
+ICE：&lt;=6.0s</t>
   </si>
   <si>
     <t>绿灯起步舒适性</t>
   </si>
   <si>
+    <t>PHEV/BEV：1.0~2.5m/s3
+ICE：1.0~2.5m/s3</t>
+  </si>
+  <si>
     <t>溜车</t>
   </si>
   <si>
     <t>行车</t>
   </si>
   <si>
-    <t>ACC active/hold/前进挡，车速&lt;=0.5kph且轮速非零，持续&gt;=0.20s</t>
+    <t>PHEV/BEV：ACC active/hold/前进挡，车速&lt;=0.5kph且轮速非零，持续&gt;=0.20s
+ICE：ACC active/hold/前进挡，车速&lt;=0.5kph且轮速非零，持续&gt;=0.20s</t>
   </si>
   <si>
     <t>无前车稳速未达到SetSpeed</t>
   </si>
   <si>
-    <t>ACC active且无override，场景&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed</t>
+    <t>PHEV/BEV：ACC active且无override，场景&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed
+ICE：ACC active且无override，场景&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed</t>
   </si>
   <si>
     <t>不合理低速</t>
   </si>
   <si>
-    <t>ACC active、无override、无红灯停车/前车风险；6s内v_max-v_min&lt;=2kph，v_min/v_max&gt;5kph，set_speed-v_max&gt;=5kph</t>
+    <t>PHEV/BEV：ACC active且无override，无前车风险/红灯停车/曲率限速；SetSpeed不变，表显车速&gt;5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph
+ICE：ACC active且无override，无前车风险/红灯停车/曲率限速；SetSpeed不变，表显车速&gt;5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph</t>
   </si>
   <si>
     <t>制动跳变导致的实车加速度抖动</t>
   </si>
   <si>
-    <t>ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2</t>
+    <t>PHEV/BEV：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2
+ICE：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2</t>
   </si>
   <si>
     <t>重制动</t>
   </si>
   <si>
-    <t>加速度&lt;-1.8m/s2，减速度跳变量&gt;=2.0m/s2，斜率&gt;=1.0，持续&gt;=0.20s，并满足jerk/深踩补充规则</t>
+    <t>PHEV/BEV：ACC active且无override；主规则：1.6s内降幅&gt;=3.0m/s2、斜率&gt;=3.0m/s3，加速度&lt;=-2.0m/s2持续&gt;=0.20s，滤波jerk&lt;=-2.0m/s3；补充：深短尖峰&lt;=-2.7m/s2、降幅&gt;=2.6m/s2、驻留&lt;=0.12s、jerk&lt;=-10，或深持续制动&lt;=-2.7m/s2、降幅&gt;=1.3m/s2、驻留&gt;=0.35s、jerk&lt;=-5
+ICE：ACC active且无override；主规则：1.6s内降幅&gt;=3.0m/s2、斜率&gt;=3.0m/s3，加速度&lt;=-2.0m/s2持续&gt;=0.20s，滤波jerk&lt;=-2.0m/s3；补充：深短尖峰&lt;=-2.7m/s2、降幅&gt;=2.6m/s2、驻留&lt;=0.12s、jerk&lt;=-10，或深持续制动&lt;=-2.7m/s2、降幅&gt;=1.3m/s2、驻留&gt;=0.35s、jerk&lt;=-5</t>
   </si>
   <si>
     <t>顿挫</t>
   </si>
   <si>
-    <t>ACC active且无override，平滑加速度振荡幅值&gt;=0.75、符号翻转&gt;=1、时长1~4s，并通过驱动/制动扭矩校验</t>
+    <t>PHEV/BEV：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，平滑加速度振荡幅值&gt;=0.75、符号翻转&gt;=1、候选时长&gt;0.5s且&lt;=4s，并通过驱动/制动扭矩校验
+ICE：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，平滑加速度振荡幅值&gt;=0.75、符号翻转&gt;=1、候选时长&gt;0.5s且&lt;=4s，并通过驱动/制动扭矩校验</t>
   </si>
   <si>
     <t>Override后顿挫</t>
   </si>
   <si>
-    <t>override释放后5s内，按顿挫规则</t>
+    <t>PHEV/BEV：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数
+ICE：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数</t>
   </si>
   <si>
     <t>Override后重制动</t>
   </si>
   <si>
-    <t>override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s</t>
+    <t>PHEV/BEV：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s
+ICE：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s</t>
   </si>
   <si>
     <t>行车断握手</t>
   </si>
   <si>
-    <t>ACC active且仲裁状态=2，持续&gt;=5s</t>
+    <t>PHEV/BEV：ACC active且仲裁状态=2，持续&gt;=5s
+ICE：ACC active且仲裁状态=2，持续&gt;=5s</t>
   </si>
   <si>
     <t>进Override后顿挫</t>
   </si>
   <si>
-    <t>ACC active且override中制动请求&lt;-0.2m/s2，按顿挫规则</t>
+    <t>PHEV/BEV：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度
+ICE：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度</t>
   </si>
   <si>
     <t>起步顿挫</t>
   </si>
   <si>
-    <t>起步1s窗口内，按顿挫规则</t>
+    <t>PHEV/BEV：起步1s窗口内，按顿挫规则
+ICE：起步3s窗口内，按顿挫规则</t>
   </si>
   <si>
     <t>ABS触发关联ACC退出</t>
   </si>
   <si>
-    <t>ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+    <t>PHEV/BEV：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+ICE：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
   </si>
   <si>
     <t>TCS触发关联ACC退出</t>
   </si>
   <si>
-    <t>TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+    <t>PHEV/BEV：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+ICE：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
   </si>
   <si>
     <t>VSE触发关联ACC退出</t>
   </si>
   <si>
-    <t>VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+    <t>PHEV/BEV：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+ICE：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
   </si>
   <si>
     <t>最大加速度（0-30 km/h）</t>
@@ -328,7 +393,8 @@
     <t>行车-无干扰加速</t>
   </si>
   <si>
-    <t>ACC 激活且无 override/前车/cut-in/红灯；停止线距离&gt;50m；Fusion 前方目标状态有效；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。</t>
+    <t>PHEV/BEV：ACC 激活且无 override/前车/cut-in/红灯；停止线距离&gt;50m；Fusion 前方目标状态有效；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。
+ICE：ACC 激活且无 override/前车/cut-in/红灯；停止线距离&gt;50m；Fusion 前方目标状态有效；SetSpeed&gt;初始车速+22km/h；无曲率限速或曲率限速高于目标车速+2km/h；0.5s平滑确认场景，30s内车速上涨20km/h且平滑车速未持续下降超过1km/h；报告事件均值。</t>
   </si>
   <si>
     <t>最大加速度（30-60 km/h）</t>
@@ -374,7 +440,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -545,6 +611,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="38">
@@ -1103,7 +1174,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1154,13 +1225,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1479,10 +1546,11 @@
     <col min="2" max="2" width="29.1818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.6363636363636" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.6363636363636" style="2" customWidth="1"/>
-    <col min="5" max="8" width="18.6363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6363636363636" style="1" customWidth="1"/>
+    <col min="6" max="8" width="13" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:8">
+    <row r="1" ht="18.5" customHeight="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1498,7 +1566,7 @@
       </c>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:8">
+    <row r="2" ht="18.5" customHeight="1" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1514,7 +1582,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:8">
+    <row r="3" ht="18.5" customHeight="1" spans="1:8">
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
@@ -1530,7 +1598,7 @@
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" ht="16.5" customHeight="1" spans="1:8">
+    <row r="4" ht="18.5" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1550,7 +1618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:8">
+    <row r="5" ht="18.5" customHeight="1" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -1568,7 +1636,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:8">
+    <row r="6" ht="51.5" customHeight="1" spans="1:8">
       <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
         <v>16</v>
@@ -1584,7 +1652,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:8">
+    <row r="7" ht="51.5" customHeight="1" spans="1:8">
       <c r="A7" s="13"/>
       <c r="B7" s="14" t="s">
         <v>19</v>
@@ -1598,7 +1666,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" ht="26" customHeight="1" spans="1:8">
+    <row r="8" ht="84.5" customHeight="1" spans="1:8">
       <c r="A8" s="13"/>
       <c r="B8" s="14" t="s">
         <v>21</v>
@@ -1612,7 +1680,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" ht="26" customHeight="1" spans="1:8">
+    <row r="9" ht="84.5" customHeight="1" spans="1:8">
       <c r="A9" s="13"/>
       <c r="B9" s="14" t="s">
         <v>23</v>
@@ -1626,7 +1694,7 @@
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
     </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:8">
+    <row r="10" ht="150.5" customHeight="1" spans="1:8">
       <c r="A10" s="13"/>
       <c r="B10" s="14" t="s">
         <v>25</v>
@@ -1642,7 +1710,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
     </row>
-    <row r="11" ht="39" customHeight="1" spans="1:8">
+    <row r="11" ht="51.5" customHeight="1" spans="1:8">
       <c r="A11" s="13"/>
       <c r="B11" s="14" t="s">
         <v>28</v>
@@ -1656,7 +1724,7 @@
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
     </row>
-    <row r="12" ht="16.5" customHeight="1" spans="1:8">
+    <row r="12" ht="51.5" customHeight="1" spans="1:8">
       <c r="A12" s="13"/>
       <c r="B12" s="14" t="s">
         <v>30</v>
@@ -1670,7 +1738,7 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
     </row>
-    <row r="13" ht="16.5" customHeight="1" spans="1:8">
+    <row r="13" ht="68" customHeight="1" spans="1:8">
       <c r="A13" s="13"/>
       <c r="B13" s="14" t="s">
         <v>32</v>
@@ -1686,7 +1754,7 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
     </row>
-    <row r="14" ht="16.5" customHeight="1" spans="1:8">
+    <row r="14" ht="68" customHeight="1" spans="1:8">
       <c r="A14" s="13"/>
       <c r="B14" s="14" t="s">
         <v>35</v>
@@ -1700,7 +1768,7 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
     </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:8">
+    <row r="15" ht="68" customHeight="1" spans="1:8">
       <c r="A15" s="13"/>
       <c r="B15" s="14" t="s">
         <v>37</v>
@@ -1714,7 +1782,7 @@
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
     </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:8">
+    <row r="16" ht="117.5" customHeight="1" spans="1:8">
       <c r="A16" s="13"/>
       <c r="B16" s="14" t="s">
         <v>39</v>
@@ -1730,7 +1798,7 @@
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
     </row>
-    <row r="17" ht="26" customHeight="1" spans="1:8">
+    <row r="17" ht="84.5" customHeight="1" spans="1:8">
       <c r="A17" s="13"/>
       <c r="B17" s="14" t="s">
         <v>42</v>
@@ -1744,7 +1812,7 @@
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
     </row>
-    <row r="18" ht="16.5" customHeight="1" spans="1:8">
+    <row r="18" ht="51.5" customHeight="1" spans="1:8">
       <c r="A18" s="13"/>
       <c r="B18" s="14" t="s">
         <v>44</v>
@@ -1758,7 +1826,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
     </row>
-    <row r="19" ht="16.5" customHeight="1" spans="1:8">
+    <row r="19" ht="51.5" customHeight="1" spans="1:8">
       <c r="A19" s="13"/>
       <c r="B19" s="14" t="s">
         <v>45</v>
@@ -1772,7 +1840,7 @@
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
     </row>
-    <row r="20" ht="16.5" customHeight="1" spans="1:8">
+    <row r="20" ht="51.5" customHeight="1" spans="1:8">
       <c r="A20" s="13"/>
       <c r="B20" s="14" t="s">
         <v>47</v>
@@ -1786,7 +1854,7 @@
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
     </row>
-    <row r="21" ht="16.5" customHeight="1" spans="1:8">
+    <row r="21" ht="35" customHeight="1" spans="1:8">
       <c r="A21" s="13"/>
       <c r="B21" s="14" t="s">
         <v>49</v>
@@ -1800,7 +1868,7 @@
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
     </row>
-    <row r="22" ht="16.5" customHeight="1" spans="1:8">
+    <row r="22" ht="35" customHeight="1" spans="1:8">
       <c r="A22" s="13"/>
       <c r="B22" s="14" t="s">
         <v>51</v>
@@ -1816,7 +1884,7 @@
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" ht="51.5" customHeight="1" spans="1:8">
       <c r="A23" s="13"/>
       <c r="B23" s="14" t="s">
         <v>54</v>
@@ -1830,7 +1898,7 @@
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" ht="35" customHeight="1" spans="1:8">
       <c r="A24" s="13"/>
       <c r="B24" s="14" t="s">
         <v>56</v>
@@ -1846,442 +1914,442 @@
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" ht="51.5" customHeight="1" spans="1:8">
       <c r="A25" s="13"/>
       <c r="B25" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="15" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
       <c r="G25" s="17"/>
       <c r="H25" s="17"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" ht="35" customHeight="1" spans="1:8">
       <c r="A26" s="13"/>
       <c r="B26" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" ht="51.5" customHeight="1" spans="1:8">
       <c r="A27" s="13"/>
       <c r="B27" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" ht="35" customHeight="1" spans="1:8">
       <c r="A28" s="13"/>
       <c r="B28" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" ht="51.5" customHeight="1" spans="1:8">
       <c r="A29" s="13"/>
       <c r="B29" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="15" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
     </row>
-    <row r="30" ht="56" spans="1:8">
+    <row r="30" ht="134" customHeight="1" spans="1:8">
       <c r="A30" s="13"/>
       <c r="B30" s="14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
       <c r="H30" s="17"/>
     </row>
-    <row r="31" ht="56" spans="1:8">
+    <row r="31" ht="150.5" customHeight="1" spans="1:8">
       <c r="A31" s="13"/>
       <c r="B31" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
       <c r="G31" s="17"/>
       <c r="H31" s="17"/>
     </row>
-    <row r="32" ht="112" spans="1:8">
+    <row r="32" ht="160" customHeight="1" spans="1:8">
       <c r="A32" s="13"/>
       <c r="B32" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
       <c r="H32" s="17"/>
     </row>
-    <row r="33" ht="84" spans="1:8">
+    <row r="33" ht="160" customHeight="1" spans="1:8">
       <c r="A33" s="13"/>
       <c r="B33" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
       <c r="G33" s="17"/>
       <c r="H33" s="17"/>
     </row>
-    <row r="34" ht="84" spans="1:8">
+    <row r="34" ht="160" customHeight="1" spans="1:8">
       <c r="A34" s="13"/>
       <c r="B34" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="17"/>
       <c r="G34" s="17"/>
       <c r="H34" s="17"/>
     </row>
-    <row r="35" ht="84" spans="1:8">
+    <row r="35" ht="160" customHeight="1" spans="1:8">
       <c r="A35" s="13"/>
       <c r="B35" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
       <c r="G35" s="17"/>
       <c r="H35" s="17"/>
     </row>
-    <row r="36" ht="28" spans="1:8">
+    <row r="36" ht="160" customHeight="1" spans="1:8">
       <c r="A36" s="13"/>
       <c r="B36" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E36" s="17"/>
       <c r="F36" s="17"/>
       <c r="G36" s="17"/>
       <c r="H36" s="17"/>
     </row>
-    <row r="37" ht="70" spans="1:8">
+    <row r="37" ht="150.5" customHeight="1" spans="1:8">
       <c r="A37" s="13"/>
       <c r="B37" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
       <c r="H37" s="17"/>
     </row>
-    <row r="38" ht="28" spans="1:8">
+    <row r="38" ht="101" customHeight="1" spans="1:8">
       <c r="A38" s="13"/>
       <c r="B38" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
       <c r="H38" s="17"/>
     </row>
-    <row r="39" ht="56" spans="1:8">
+    <row r="39" ht="150.5" customHeight="1" spans="1:8">
       <c r="A39" s="13"/>
       <c r="B39" s="14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E39" s="17"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
       <c r="H39" s="17"/>
     </row>
-    <row r="40" ht="28" spans="1:8">
+    <row r="40" ht="68" customHeight="1" spans="1:8">
       <c r="A40" s="13"/>
       <c r="B40" s="14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
     </row>
-    <row r="41" ht="70" spans="1:8">
+    <row r="41" ht="160" customHeight="1" spans="1:8">
       <c r="A41" s="13"/>
       <c r="B41" s="14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E41" s="17"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
       <c r="H41" s="17"/>
     </row>
-    <row r="42" ht="70" spans="1:8">
+    <row r="42" ht="160" customHeight="1" spans="1:8">
       <c r="A42" s="13"/>
       <c r="B42" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
       <c r="G42" s="17"/>
       <c r="H42" s="17"/>
     </row>
-    <row r="43" ht="70" spans="1:8">
+    <row r="43" ht="160" customHeight="1" spans="1:8">
       <c r="A43" s="16"/>
       <c r="B43" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
       <c r="G43" s="17"/>
       <c r="H43" s="17"/>
     </row>
-    <row r="44" ht="196" spans="1:8">
-      <c r="A44" s="20" t="s">
-        <v>69</v>
+    <row r="44" ht="160" customHeight="1" spans="1:8">
+      <c r="A44" s="17" t="s">
+        <v>71</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
       <c r="G44" s="17"/>
       <c r="H44" s="17"/>
     </row>
-    <row r="45" ht="196" spans="1:8">
-      <c r="A45" s="22"/>
+    <row r="45" ht="160" customHeight="1" spans="1:8">
+      <c r="A45" s="13"/>
       <c r="B45" s="14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E45" s="17"/>
       <c r="F45" s="17"/>
       <c r="G45" s="17"/>
       <c r="H45" s="17"/>
     </row>
-    <row r="46" ht="196" spans="1:8">
-      <c r="A46" s="22"/>
+    <row r="46" ht="160" customHeight="1" spans="1:8">
+      <c r="A46" s="13"/>
       <c r="B46" s="14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C46" s="13"/>
       <c r="D46" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
       <c r="G46" s="17"/>
       <c r="H46" s="17"/>
     </row>
-    <row r="47" ht="196" spans="1:8">
-      <c r="A47" s="22"/>
+    <row r="47" ht="160" customHeight="1" spans="1:8">
+      <c r="A47" s="13"/>
       <c r="B47" s="14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C47" s="13"/>
       <c r="D47" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E47" s="17"/>
       <c r="F47" s="17"/>
       <c r="G47" s="17"/>
       <c r="H47" s="17"/>
     </row>
-    <row r="48" ht="196" spans="1:8">
-      <c r="A48" s="22"/>
+    <row r="48" ht="160" customHeight="1" spans="1:8">
+      <c r="A48" s="13"/>
       <c r="B48" s="14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E48" s="17"/>
       <c r="F48" s="17"/>
       <c r="G48" s="17"/>
       <c r="H48" s="17"/>
     </row>
-    <row r="49" ht="196" spans="1:8">
-      <c r="A49" s="22"/>
+    <row r="49" ht="160" customHeight="1" spans="1:8">
+      <c r="A49" s="13"/>
       <c r="B49" s="14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E49" s="17"/>
       <c r="F49" s="17"/>
       <c r="G49" s="17"/>
       <c r="H49" s="17"/>
     </row>
-    <row r="50" ht="196" spans="1:8">
-      <c r="A50" s="22"/>
+    <row r="50" ht="160" customHeight="1" spans="1:8">
+      <c r="A50" s="13"/>
       <c r="B50" s="14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E50" s="17"/>
       <c r="F50" s="17"/>
       <c r="G50" s="17"/>
       <c r="H50" s="17"/>
     </row>
-    <row r="51" ht="196" spans="1:8">
-      <c r="A51" s="22"/>
+    <row r="51" ht="160" customHeight="1" spans="1:8">
+      <c r="A51" s="13"/>
       <c r="B51" s="14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C51" s="13"/>
       <c r="D51" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E51" s="17"/>
       <c r="F51" s="17"/>
       <c r="G51" s="17"/>
       <c r="H51" s="17"/>
     </row>
-    <row r="52" ht="196" spans="1:8">
-      <c r="A52" s="22"/>
+    <row r="52" ht="160" customHeight="1" spans="1:8">
+      <c r="A52" s="13"/>
       <c r="B52" s="14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C52" s="13"/>
       <c r="D52" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E52" s="17"/>
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
       <c r="H52" s="17"/>
     </row>
-    <row r="53" ht="196" spans="1:8">
-      <c r="A53" s="22"/>
+    <row r="53" ht="160" customHeight="1" spans="1:8">
+      <c r="A53" s="13"/>
       <c r="B53" s="14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C53" s="13"/>
       <c r="D53" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E53" s="17"/>
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
       <c r="H53" s="17"/>
     </row>
-    <row r="54" ht="196" spans="1:8">
-      <c r="A54" s="22"/>
+    <row r="54" ht="160" customHeight="1" spans="1:8">
+      <c r="A54" s="13"/>
       <c r="B54" s="14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C54" s="13"/>
       <c r="D54" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E54" s="17"/>
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
       <c r="H54" s="17"/>
     </row>
-    <row r="55" ht="196" spans="1:8">
-      <c r="A55" s="22"/>
+    <row r="55" ht="160" customHeight="1" spans="1:8">
+      <c r="A55" s="16"/>
       <c r="B55" s="14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C55" s="16"/>
       <c r="D55" s="19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E55" s="17"/>
       <c r="F55" s="17"/>
@@ -2316,6 +2384,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/CompareKPI_United/templates/template_MMT.xlsx
+++ b/CompareKPI_United/templates/template_MMT.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.27272727272727" customWidth="1" style="1" min="1" max="1"/>
@@ -1663,7 +1663,7 @@
           <t>跟车刹停风险</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n"/>
+      <c r="C20" s="16" t="n"/>
       <c r="D20" s="15" t="inlineStr">
         <is>
           <t>ICE：TTC&gt;=1.5s
@@ -1680,15 +1680,19 @@
       <c r="A21" s="13" t="n"/>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>跟车刹停波动</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="n"/>
+          <t>跟车起步响应时延</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>行车-跟车起步</t>
+        </is>
+      </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>ICE：&lt;=3次
-PHEV：&lt;=3次
-BEV：&lt;=3次</t>
+          <t>ICE：&lt;=2.8s
+PHEV：&lt;=2.5s
+BEV：&lt;=2.5s</t>
         </is>
       </c>
       <c r="E21" s="12" t="n"/>
@@ -1696,43 +1700,43 @@
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
     </row>
-    <row r="22" ht="35" customHeight="1" s="1">
+    <row r="22" ht="51.5" customHeight="1" s="1">
       <c r="A22" s="13" t="n"/>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>跟车起步响应时延</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>行车-跟车起步</t>
-        </is>
-      </c>
+          <t>跟车起步舒适性</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n"/>
       <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>ICE：&lt;=2.8s
-PHEV：&lt;=2.5s
-BEV：&lt;=2.5s</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-    </row>
-    <row r="23" ht="51.5" customHeight="1" s="1">
-      <c r="A23" s="13" t="n"/>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>跟车起步舒适性</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>ICE：1.0~1.5m/s3
 PHEV：1.0~1.5m/s3
 BEV：1.0~1.5m/s3</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
+    </row>
+    <row r="23" ht="35" customHeight="1" s="1">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>红灯刹停距停止线距离</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>行车-红灯刹停</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>ICE：1.5~3.5m
+PHEV：1.5~3.5m
+BEV：1.5~3.5m</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -1740,23 +1744,19 @@
       <c r="G23" s="17" t="n"/>
       <c r="H23" s="17" t="n"/>
     </row>
-    <row r="24" ht="35" customHeight="1" s="1">
+    <row r="24" ht="51.5" customHeight="1" s="1">
       <c r="A24" s="13" t="n"/>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>红灯刹停距停止线距离</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>行车-红灯刹停</t>
-        </is>
-      </c>
+          <t>红灯刹停舒适性</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n"/>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>ICE：1.5~3.5m
-PHEV：1.5~3.5m
-BEV：1.5~3.5m</t>
+          <t>ICE：&gt;=-2.3m/s3
+PHEV：&gt;=-2m/s3
+BEV：&gt;=-2m/s3</t>
         </is>
       </c>
       <c r="E24" s="17" t="n"/>
@@ -1764,19 +1764,23 @@
       <c r="G24" s="17" t="n"/>
       <c r="H24" s="17" t="n"/>
     </row>
-    <row r="25" ht="51.5" customHeight="1" s="1">
+    <row r="25" ht="35" customHeight="1" s="1">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>红灯刹停舒适性</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="n"/>
+          <t>绿灯起步响应时延</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>行车-绿灯起步</t>
+        </is>
+      </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>ICE：&gt;=-2.3m/s3
-PHEV：&gt;=-2m/s3
-BEV：&gt;=-2m/s3</t>
+          <t>ICE：&lt;=1.7s
+PHEV：&lt;=1.5s
+BEV：&lt;=1.5s</t>
         </is>
       </c>
       <c r="E25" s="17" t="n"/>
@@ -1784,23 +1788,19 @@
       <c r="G25" s="17" t="n"/>
       <c r="H25" s="17" t="n"/>
     </row>
-    <row r="26" ht="35" customHeight="1" s="1">
+    <row r="26" ht="51.5" customHeight="1" s="1">
       <c r="A26" s="13" t="n"/>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>绿灯起步响应时延</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>行车-绿灯起步</t>
-        </is>
-      </c>
+          <t>绿灯起步最大加速度</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n"/>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>ICE：&lt;=1.7s
-PHEV：&lt;=1.5s
-BEV：&lt;=1.5s</t>
+          <t>ICE：1.0~2.3m/s2
+PHEV：1.0~2.3m/s2
+BEV：1.0~2.3m/s2</t>
         </is>
       </c>
       <c r="E26" s="17" t="n"/>
@@ -1808,19 +1808,19 @@
       <c r="G26" s="17" t="n"/>
       <c r="H26" s="17" t="n"/>
     </row>
-    <row r="27" ht="51.5" customHeight="1" s="1">
+    <row r="27" ht="35" customHeight="1" s="1">
       <c r="A27" s="13" t="n"/>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>绿灯起步最大加速度</t>
+          <t>绿灯起步加速时间</t>
         </is>
       </c>
       <c r="C27" s="13" t="n"/>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>ICE：1.0~2.3m/s2
-PHEV：1.0~2.3m/s2
-BEV：1.0~2.3m/s2</t>
+          <t>ICE：&lt;=6.0s
+PHEV：&lt;=6.0s
+BEV：&lt;=6.0s</t>
         </is>
       </c>
       <c r="E27" s="17" t="n"/>
@@ -1828,19 +1828,19 @@
       <c r="G27" s="17" t="n"/>
       <c r="H27" s="17" t="n"/>
     </row>
-    <row r="28" ht="35" customHeight="1" s="1">
+    <row r="28" ht="51.5" customHeight="1" s="1">
       <c r="A28" s="13" t="n"/>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>绿灯起步加速时间</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="n"/>
+          <t>绿灯起步舒适性</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n"/>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>ICE：&lt;=6.0s
-PHEV：&lt;=6.0s
-BEV：&lt;=6.0s</t>
+          <t>ICE：1.0~2.5m/s3
+PHEV：1.0~2.5m/s3
+BEV：1.0~2.5m/s3</t>
         </is>
       </c>
       <c r="E28" s="17" t="n"/>
@@ -1848,19 +1848,23 @@
       <c r="G28" s="17" t="n"/>
       <c r="H28" s="17" t="n"/>
     </row>
-    <row r="29" ht="51.5" customHeight="1" s="1">
+    <row r="29" ht="134" customHeight="1" s="1">
       <c r="A29" s="13" t="n"/>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>绿灯起步舒适性</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>ICE：1.0~2.5m/s3
-PHEV：1.0~2.5m/s3
-BEV：1.0~2.5m/s3</t>
+          <t>溜车</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>行车</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>ICE：ACC active/hold/前进挡，车速&lt;=0.5kph且轮速非零，持续&gt;=0.20s
+PHEV：ACC active/hold/前进挡，车速&lt;=0.5kph且轮速非零，持续&gt;=0.20s
+BEV：ACC active/hold/前进挡，车速&lt;=0.5kph且轮速非零，持续&gt;=0.20s</t>
         </is>
       </c>
       <c r="E29" s="17" t="n"/>
@@ -1868,23 +1872,19 @@
       <c r="G29" s="17" t="n"/>
       <c r="H29" s="17" t="n"/>
     </row>
-    <row r="30" ht="134" customHeight="1" s="1">
+    <row r="30" ht="150.5" customHeight="1" s="1">
       <c r="A30" s="13" t="n"/>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>溜车</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>行车</t>
-        </is>
-      </c>
+          <t>无前车稳速未达到SetSpeed</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n"/>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>ICE：ACC active/hold/前进挡，车速&lt;=0.5kph且轮速非零，持续&gt;=0.20s
-PHEV：ACC active/hold/前进挡，车速&lt;=0.5kph且轮速非零，持续&gt;=0.20s
-BEV：ACC active/hold/前进挡，车速&lt;=0.5kph且轮速非零，持续&gt;=0.20s</t>
+          <t>ICE：ACC active且无override，场景&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed
+PHEV：ACC active且无override，场景&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed
+BEV：ACC active且无override，场景&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed</t>
         </is>
       </c>
       <c r="E30" s="17" t="n"/>
@@ -1892,19 +1892,19 @@
       <c r="G30" s="17" t="n"/>
       <c r="H30" s="17" t="n"/>
     </row>
-    <row r="31" ht="150.5" customHeight="1" s="1">
+    <row r="31" ht="160" customHeight="1" s="1">
       <c r="A31" s="13" t="n"/>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>无前车稳速未达到SetSpeed</t>
+          <t>不合理低速</t>
         </is>
       </c>
       <c r="C31" s="13" t="n"/>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>ICE：ACC active且无override，场景&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed
-PHEV：ACC active且无override，场景&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed
-BEV：ACC active且无override，场景&gt;=8s、车速波动&lt;=2kph，未达到SetSpeed</t>
+          <t>ICE：ACC active且无override，无前车风险/红灯停车/曲率限速；SetSpeed不变，表显车速&gt;5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph
+PHEV：ACC active且无override，无前车风险/红灯停车/曲率限速；SetSpeed不变，表显车速&gt;5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph
+BEV：ACC active且无override，无前车风险/红灯停车/曲率限速；SetSpeed不变，表显车速&gt;5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph</t>
         </is>
       </c>
       <c r="E31" s="17" t="n"/>
@@ -1916,15 +1916,15 @@
       <c r="A32" s="13" t="n"/>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>不合理低速</t>
+          <t>制动跳变导致的实车加速度抖动</t>
         </is>
       </c>
       <c r="C32" s="13" t="n"/>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>ICE：ACC active且无override，无前车风险/红灯停车/曲率限速；SetSpeed不变，表显车速&gt;5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph
-PHEV：ACC active且无override，无前车风险/红灯停车/曲率限速；SetSpeed不变，表显车速&gt;5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph
-BEV：ACC active且无override，无前车风险/红灯停车/曲率限速；SetSpeed不变，表显车速&gt;5kph且稳定&gt;=8s，波动&lt;1.5kph，SetSpeed-v_max&gt;=8kph</t>
+          <t>ICE：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2
+PHEV：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2
+BEV：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2</t>
         </is>
       </c>
       <c r="E32" s="17" t="n"/>
@@ -1936,15 +1936,15 @@
       <c r="A33" s="13" t="n"/>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>制动跳变导致的实车加速度抖动</t>
+          <t>重制动</t>
         </is>
       </c>
       <c r="C33" s="13" t="n"/>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>ICE：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2
-PHEV：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2
-BEV：ACC active且无override，AutoBrake 2-&gt;1-&gt;2中间态&lt;=0.10s，随后1s减速度波动&gt;2.0m/s2</t>
+          <t>ICE：ACC active且无override；主规则：1.6s内降幅&gt;=3.0m/s2、斜率&gt;=3.0m/s3，加速度&lt;=-2.0m/s2持续&gt;=0.20s，滤波jerk&lt;=-2.0m/s3；补充：深短尖峰&lt;=-2.7m/s2、降幅&gt;=2.6m/s2、驻留&lt;=0.12s、jerk&lt;=-10，或深持续制动&lt;=-2.7m/s2、降幅&gt;=1.3m/s2、驻留&gt;=0.35s、jerk&lt;=-5
+PHEV：ACC active且无override；主规则：1.6s内降幅&gt;=3.0m/s2、斜率&gt;=3.0m/s3，加速度&lt;=-2.0m/s2持续&gt;=0.20s，滤波jerk&lt;=-2.0m/s3；补充：深短尖峰&lt;=-2.7m/s2、降幅&gt;=2.6m/s2、驻留&lt;=0.12s、jerk&lt;=-10，或深持续制动&lt;=-2.7m/s2、降幅&gt;=1.3m/s2、驻留&gt;=0.35s、jerk&lt;=-5
+BEV：ACC active且无override；主规则：1.6s内降幅&gt;=3.0m/s2、斜率&gt;=3.0m/s3，加速度&lt;=-2.0m/s2持续&gt;=0.20s，滤波jerk&lt;=-2.0m/s3；补充：深短尖峰&lt;=-2.7m/s2、降幅&gt;=2.6m/s2、驻留&lt;=0.12s、jerk&lt;=-10，或深持续制动&lt;=-2.7m/s2、降幅&gt;=1.3m/s2、驻留&gt;=0.35s、jerk&lt;=-5</t>
         </is>
       </c>
       <c r="E33" s="17" t="n"/>
@@ -1956,15 +1956,15 @@
       <c r="A34" s="13" t="n"/>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>重制动</t>
+          <t>顿挫</t>
         </is>
       </c>
       <c r="C34" s="13" t="n"/>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>ICE：ACC active且无override；主规则：1.6s内降幅&gt;=3.0m/s2、斜率&gt;=3.0m/s3，加速度&lt;=-2.0m/s2持续&gt;=0.20s，滤波jerk&lt;=-2.0m/s3；补充：深短尖峰&lt;=-2.7m/s2、降幅&gt;=2.6m/s2、驻留&lt;=0.12s、jerk&lt;=-10，或深持续制动&lt;=-2.7m/s2、降幅&gt;=1.3m/s2、驻留&gt;=0.35s、jerk&lt;=-5
-PHEV：ACC active且无override；主规则：1.6s内降幅&gt;=3.0m/s2、斜率&gt;=3.0m/s3，加速度&lt;=-2.0m/s2持续&gt;=0.20s，滤波jerk&lt;=-2.0m/s3；补充：深短尖峰&lt;=-2.7m/s2、降幅&gt;=2.6m/s2、驻留&lt;=0.12s、jerk&lt;=-10，或深持续制动&lt;=-2.7m/s2、降幅&gt;=1.3m/s2、驻留&gt;=0.35s、jerk&lt;=-5
-BEV：ACC active且无override；主规则：1.6s内降幅&gt;=3.0m/s2、斜率&gt;=3.0m/s3，加速度&lt;=-2.0m/s2持续&gt;=0.20s，滤波jerk&lt;=-2.0m/s3；补充：深短尖峰&lt;=-2.7m/s2、降幅&gt;=2.6m/s2、驻留&lt;=0.12s、jerk&lt;=-10，或深持续制动&lt;=-2.7m/s2、降幅&gt;=1.3m/s2、驻留&gt;=0.35s、jerk&lt;=-5</t>
+          <t>ICE：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，平滑加速度振荡幅值&gt;=0.75、符号翻转&gt;=1、候选时长&gt;0.5s且&lt;=4s，并通过驱动/制动扭矩校验
+PHEV：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，平滑加速度振荡幅值&gt;=0.75、符号翻转&gt;=1、候选时长&gt;0.5s且&lt;=4s，并通过驱动/制动扭矩校验
+BEV：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，平滑加速度振荡幅值&gt;=0.75、符号翻转&gt;=1、候选时长&gt;0.5s且&lt;=4s，并通过驱动/制动扭矩校验</t>
         </is>
       </c>
       <c r="E34" s="17" t="n"/>
@@ -1976,15 +1976,15 @@
       <c r="A35" s="13" t="n"/>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>顿挫</t>
+          <t>Override后顿挫</t>
         </is>
       </c>
       <c r="C35" s="13" t="n"/>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>ICE：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，平滑加速度振荡幅值&gt;=0.75、符号翻转&gt;=1、候选时长&gt;0.5s且&lt;=4s，并通过驱动/制动扭矩校验
-PHEV：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，平滑加速度振荡幅值&gt;=0.75、符号翻转&gt;=1、候选时长&gt;0.5s且&lt;=4s，并通过驱动/制动扭矩校验
-BEV：仅统计排除Override后顿挫（释放后2s）、进Override后顿挫及起步顿挫（ACC激活后1s）场景后的顿挫；ACC active且无override，平滑加速度振荡幅值&gt;=0.75、符号翻转&gt;=1、候选时长&gt;0.5s且&lt;=4s，并通过驱动/制动扭矩校验</t>
+          <t>ICE：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数
+PHEV：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数
+BEV：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数</t>
         </is>
       </c>
       <c r="E35" s="17" t="n"/>
@@ -1992,19 +1992,19 @@
       <c r="G35" s="17" t="n"/>
       <c r="H35" s="17" t="n"/>
     </row>
-    <row r="36" ht="160" customHeight="1" s="1">
+    <row r="36" ht="150.5" customHeight="1" s="1">
       <c r="A36" s="13" t="n"/>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Override后顿挫</t>
+          <t>Override后重制动</t>
         </is>
       </c>
       <c r="C36" s="13" t="n"/>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>ICE：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数
-PHEV：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数
-BEV：override释放后完整2s窗口（数据不足2s丢弃），窗口内持续ACC active且无再次override；按顿挫规则检测，按窗口计数</t>
+          <t>ICE：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s
+PHEV：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s
+BEV：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s</t>
         </is>
       </c>
       <c r="E36" s="17" t="n"/>
@@ -2012,19 +2012,19 @@
       <c r="G36" s="17" t="n"/>
       <c r="H36" s="17" t="n"/>
     </row>
-    <row r="37" ht="150.5" customHeight="1" s="1">
+    <row r="37" ht="101" customHeight="1" s="1">
       <c r="A37" s="13" t="n"/>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Override后重制动</t>
+          <t>行车断握手</t>
         </is>
       </c>
       <c r="C37" s="13" t="n"/>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>ICE：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s
-PHEV：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s
-BEV：override释放后5s内，加速度&lt;-2.0m/s2且jerk&lt;-3.0m/s3，持续&gt;=0.20s</t>
+          <t>ICE：ACC active且仲裁状态=2，持续&gt;=5s
+PHEV：ACC active且仲裁状态=2，持续&gt;=5s
+BEV：ACC active且仲裁状态=2，持续&gt;=5s</t>
         </is>
       </c>
       <c r="E37" s="17" t="n"/>
@@ -2032,19 +2032,19 @@
       <c r="G37" s="17" t="n"/>
       <c r="H37" s="17" t="n"/>
     </row>
-    <row r="38" ht="101" customHeight="1" s="1">
+    <row r="38" ht="150.5" customHeight="1" s="1">
       <c r="A38" s="13" t="n"/>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>行车断握手</t>
+          <t>进Override后顿挫</t>
         </is>
       </c>
       <c r="C38" s="13" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>ICE：ACC active且仲裁状态=2，持续&gt;=5s
-PHEV：ACC active且仲裁状态=2，持续&gt;=5s
-BEV：ACC active且仲裁状态=2，持续&gt;=5s</t>
+          <t>ICE：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度
+PHEV：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度
+BEV：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度</t>
         </is>
       </c>
       <c r="E38" s="17" t="n"/>
@@ -2052,19 +2052,19 @@
       <c r="G38" s="17" t="n"/>
       <c r="H38" s="17" t="n"/>
     </row>
-    <row r="39" ht="150.5" customHeight="1" s="1">
+    <row r="39" ht="68" customHeight="1" s="1">
       <c r="A39" s="13" t="n"/>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>进Override后顿挫</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="n"/>
+          <t>起步顿挫</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>ICE：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度
-PHEV：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度
-BEV：ACC active且override中，油门&gt;0，按顿挫规则；不限制制动请求加速度</t>
+          <t>ICE：起步3s窗口内，按顿挫规则
+PHEV：起步1s窗口内，按顿挫规则
+BEV：起步1s窗口内，按顿挫规则</t>
         </is>
       </c>
       <c r="E39" s="17" t="n"/>
@@ -2072,19 +2072,19 @@
       <c r="G39" s="17" t="n"/>
       <c r="H39" s="17" t="n"/>
     </row>
-    <row r="40" ht="68" customHeight="1" s="1">
+    <row r="40" ht="160" customHeight="1" s="1">
       <c r="A40" s="13" t="n"/>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>起步顿挫</t>
+          <t>ABS触发关联ACC退出</t>
         </is>
       </c>
       <c r="C40" s="16" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>ICE：起步3s窗口内，按顿挫规则
-PHEV：起步1s窗口内，按顿挫规则
-BEV：起步1s窗口内，按顿挫规则</t>
+          <t>ICE：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+PHEV：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+BEV：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
         </is>
       </c>
       <c r="E40" s="17" t="n"/>
@@ -2096,15 +2096,15 @@
       <c r="A41" s="13" t="n"/>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>ABS触发关联ACC退出</t>
+          <t>TCS触发关联ACC退出</t>
         </is>
       </c>
       <c r="C41" s="16" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>ICE：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-PHEV：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-BEV：ABS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+          <t>ICE：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+PHEV：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+BEV：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
         </is>
       </c>
       <c r="E41" s="17" t="n"/>
@@ -2113,18 +2113,18 @@
       <c r="H41" s="17" t="n"/>
     </row>
     <row r="42" ht="160" customHeight="1" s="1">
-      <c r="A42" s="13" t="n"/>
+      <c r="A42" s="16" t="n"/>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>TCS触发关联ACC退出</t>
+          <t>VSE触发关联ACC退出</t>
         </is>
       </c>
       <c r="C42" s="16" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>ICE：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-PHEV：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-BEV：TCS由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+          <t>ICE：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+PHEV：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
+BEV：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
         </is>
       </c>
       <c r="E42" s="17" t="n"/>
@@ -2133,18 +2133,26 @@
       <c r="H42" s="17" t="n"/>
     </row>
     <row r="43" ht="160" customHeight="1" s="1">
-      <c r="A43" s="16" t="n"/>
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>行车</t>
+        </is>
+      </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>VSE触发关联ACC退出</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="n"/>
+          <t>最大加速度（0-30 km/h）</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>行车-无干扰加速</t>
+        </is>
+      </c>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>ICE：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-PHEV：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数
-BEV：VSE由未激活转为激活时ACC已激活，且1秒内ACC由激活转为未激活；按关联退出事件计数</t>
+          <t>ICE：事件最大加速度：1.5~2.5 m/s²（含边界）
+PHEV：事件最大加速度：1.5~2.5 m/s²（含边界）
+BEV：事件最大加速度：1.5~2.5 m/s²（含边界）</t>
         </is>
       </c>
       <c r="E43" s="17" t="n"/>
@@ -2153,21 +2161,13 @@
       <c r="H43" s="17" t="n"/>
     </row>
     <row r="44" ht="160" customHeight="1" s="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>行车</t>
-        </is>
-      </c>
+      <c r="A44" s="13" t="n"/>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>最大加速度（0-30 km/h）</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>行车-无干扰加速</t>
-        </is>
-      </c>
+          <t>最大加速度（30-60 km/h）</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
           <t>ICE：事件最大加速度：1.5~2.5 m/s²（含边界）
@@ -2184,7 +2184,7 @@
       <c r="A45" s="13" t="n"/>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>最大加速度（30-60 km/h）</t>
+          <t>最大加速度（60-90 km/h）</t>
         </is>
       </c>
       <c r="C45" s="13" t="n"/>
@@ -2204,7 +2204,7 @@
       <c r="A46" s="13" t="n"/>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>最大加速度（60-90 km/h）</t>
+          <t>最大加速度（&gt;=90 km/h）</t>
         </is>
       </c>
       <c r="C46" s="13" t="n"/>
@@ -2224,15 +2224,15 @@
       <c r="A47" s="13" t="n"/>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>最大加速度（&gt;=90 km/h）</t>
+          <t>加速建立时间（0-30 km/h）</t>
         </is>
       </c>
       <c r="C47" s="13" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>ICE：事件最大加速度：1.5~2.5 m/s²（含边界）
-PHEV：事件最大加速度：1.5~2.5 m/s²（含边界）
-BEV：事件最大加速度：1.5~2.5 m/s²（含边界）</t>
+          <t>ICE：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
+PHEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
+BEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s</t>
         </is>
       </c>
       <c r="E47" s="17" t="n"/>
@@ -2244,7 +2244,7 @@
       <c r="A48" s="13" t="n"/>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>加速建立时间（0-30 km/h）</t>
+          <t>加速建立时间（30-60 km/h）</t>
         </is>
       </c>
       <c r="C48" s="13" t="n"/>
@@ -2264,7 +2264,7 @@
       <c r="A49" s="13" t="n"/>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>加速建立时间（30-60 km/h）</t>
+          <t>加速建立时间（60-90 km/h）</t>
         </is>
       </c>
       <c r="C49" s="13" t="n"/>
@@ -2284,7 +2284,7 @@
       <c r="A50" s="13" t="n"/>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>加速建立时间（60-90 km/h）</t>
+          <t>加速建立时间（&gt;=90 km/h）</t>
         </is>
       </c>
       <c r="C50" s="13" t="n"/>
@@ -2304,15 +2304,15 @@
       <c r="A51" s="13" t="n"/>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>加速建立时间（&gt;=90 km/h）</t>
+          <t>平均加速度（0-30 km/h）</t>
         </is>
       </c>
       <c r="C51" s="13" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>ICE：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
-PHEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s
-BEV：加速建立时间（加速度首次&gt;0.2 m/s²至峰值）：&lt;3.5 s</t>
+          <t>ICE：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
+PHEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
+BEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²</t>
         </is>
       </c>
       <c r="E51" s="17" t="n"/>
@@ -2324,7 +2324,7 @@
       <c r="A52" s="13" t="n"/>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>平均加速度（0-30 km/h）</t>
+          <t>平均加速度（30-60 km/h）</t>
         </is>
       </c>
       <c r="C52" s="13" t="n"/>
@@ -2344,7 +2344,7 @@
       <c r="A53" s="13" t="n"/>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>平均加速度（30-60 km/h）</t>
+          <t>平均加速度（60-90 km/h）</t>
         </is>
       </c>
       <c r="C53" s="13" t="n"/>
@@ -2361,13 +2361,13 @@
       <c r="H53" s="17" t="n"/>
     </row>
     <row r="54" ht="160" customHeight="1" s="1">
-      <c r="A54" s="13" t="n"/>
+      <c r="A54" s="16" t="n"/>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>平均加速度（60-90 km/h）</t>
-        </is>
-      </c>
-      <c r="C54" s="13" t="n"/>
+          <t>平均加速度（&gt;=90 km/h）</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
           <t>ICE：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
@@ -2380,48 +2380,28 @@
       <c r="G54" s="17" t="n"/>
       <c r="H54" s="17" t="n"/>
     </row>
-    <row r="55" ht="160" customHeight="1" s="1">
-      <c r="A55" s="16" t="n"/>
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>平均加速度（&gt;=90 km/h）</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="n"/>
-      <c r="D55" s="19" t="inlineStr">
-        <is>
-          <t>ICE：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
-PHEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²
-BEV：平均加速度（车速增量/事件耗时）：&gt;1.5 m/s²</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="n"/>
-      <c r="F55" s="17" t="n"/>
-      <c r="G55" s="17" t="n"/>
-      <c r="H55" s="17" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A5:A42"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="A44:A55"/>
-    <mergeCell ref="C22:C23"/>
     <mergeCell ref="C13:C15"/>
+    <mergeCell ref="A43:A54"/>
+    <mergeCell ref="C25:C28"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="E5:H5"/>
-    <mergeCell ref="G3:H3"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C44:C55"/>
+    <mergeCell ref="C23:C24"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="C10:C12"/>
-    <mergeCell ref="A5:A43"/>
+    <mergeCell ref="C43:C54"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="C30:C40"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="C16:C20"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C29:C39"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="E3:F3"/>
   </mergeCells>

--- a/CompareKPI_United/templates/template_MMT.xlsx
+++ b/CompareKPI_United/templates/template_MMT.xlsx
@@ -1434,9 +1434,9 @@
       <c r="C9" s="16" t="n"/>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>ICE：首次acc&gt;0.2到最大acc：1.0~4.0s
-PHEV：首次acc&gt;0.2到最大acc：1.0~3.5s
-BEV：首次acc&gt;0.2到最大acc：1.0~3.5s</t>
+          <t>ICE：&lt;=4s
+PHEV：&lt;=3.5s
+BEV：&lt;=3.5s</t>
         </is>
       </c>
       <c r="E9" s="12" t="n"/>
@@ -1522,9 +1522,9 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>ICE：速度波动&lt;=0.6m/s
-PHEV：速度波动&lt;=0.3m/s
-BEV：速度波动&lt;=0.3m/s</t>
+          <t>ICE：仪表车速极差&lt;=0.6km/h
+PHEV：仪表车速极差&lt;=0.3km/h
+BEV：仪表车速极差&lt;=0.3km/h</t>
         </is>
       </c>
       <c r="E13" s="12" t="n"/>
@@ -1606,9 +1606,9 @@
       <c r="C17" s="13" t="n"/>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>ICE：刹停完成时距前车距离：3~4m
-PHEV：刹停完成时距前车距离：3~4m
-BEV：刹停完成时距前车距离：3~4m</t>
+          <t>ICE：3~4m
+PHEV：3~4m
+BEV：3~4m</t>
         </is>
       </c>
       <c r="E17" s="12" t="n"/>
@@ -1710,9 +1710,9 @@
       <c r="C22" s="16" t="n"/>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>ICE：1.0~1.5m/s3
-PHEV：1.0~1.5m/s3
-BEV：1.0~1.5m/s3</t>
+          <t>ICE：最大jerk&lt;=1.5m/s3
+PHEV：最大jerk&lt;=1.5m/s3
+BEV：最大jerk&lt;=1.5m/s3</t>
         </is>
       </c>
       <c r="E22" s="17" t="n"/>
@@ -1838,9 +1838,9 @@
       <c r="C28" s="16" t="n"/>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>ICE：1.0~2.5m/s3
-PHEV：1.0~2.5m/s3
-BEV：1.0~2.5m/s3</t>
+          <t>ICE：最大jerk&lt;=2.5m/s3
+PHEV：最大jerk&lt;=2.5m/s3
+BEV：最大jerk&lt;=2.5m/s3</t>
         </is>
       </c>
       <c r="E28" s="17" t="n"/>
